--- a/backend/wp_templates/N/N1 递延所得税资产.xlsx
+++ b/backend/wp_templates/N/N1 递延所得税资产.xlsx
@@ -8694,7 +8694,7 @@
       <c r="F11" s="365" t="n"/>
       <c r="G11" s="365" t="n"/>
       <c r="H11" s="367">
-        <f>F11+E11</f>
+        <f>E11+F11+G11</f>
         <v/>
       </c>
       <c r="I11" s="365" t="n"/>
@@ -8706,7 +8706,7 @@
       <c r="L11" s="365" t="n"/>
       <c r="M11" s="365" t="n"/>
       <c r="N11" s="368">
-        <f>L11+K11</f>
+        <f>K11+L11+M11</f>
         <v/>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       <c r="F12" s="365" t="n"/>
       <c r="G12" s="365" t="n"/>
       <c r="H12" s="367">
-        <f>F12+E12</f>
+        <f>E12+F12+G12</f>
         <v/>
       </c>
       <c r="I12" s="365" t="n"/>
@@ -8742,7 +8742,7 @@
       <c r="L12" s="365" t="n"/>
       <c r="M12" s="365" t="n"/>
       <c r="N12" s="368">
-        <f>L12+K12</f>
+        <f>K12+L12+M12</f>
         <v/>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       <c r="F13" s="365" t="n"/>
       <c r="G13" s="365" t="n"/>
       <c r="H13" s="367">
-        <f>F13+E13</f>
+        <f>E13+F13+G13</f>
         <v/>
       </c>
       <c r="I13" s="365" t="n"/>
@@ -8778,7 +8778,7 @@
       <c r="L13" s="365" t="n"/>
       <c r="M13" s="365" t="n"/>
       <c r="N13" s="368">
-        <f>L13+K13</f>
+        <f>K13+L13+M13</f>
         <v/>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
       <c r="F14" s="365" t="n"/>
       <c r="G14" s="365" t="n"/>
       <c r="H14" s="367">
-        <f>F14+E14</f>
+        <f>E14+F14+G14</f>
         <v/>
       </c>
       <c r="I14" s="365" t="n"/>
@@ -8814,7 +8814,7 @@
       <c r="L14" s="365" t="n"/>
       <c r="M14" s="365" t="n"/>
       <c r="N14" s="368">
-        <f>L14+K14</f>
+        <f>K14+L14+M14</f>
         <v/>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       <c r="F15" s="365" t="n"/>
       <c r="G15" s="365" t="n"/>
       <c r="H15" s="367">
-        <f>F15+E15</f>
+        <f>E15+F15+G15</f>
         <v/>
       </c>
       <c r="I15" s="365" t="n"/>
@@ -8850,7 +8850,7 @@
       <c r="L15" s="365" t="n"/>
       <c r="M15" s="365" t="n"/>
       <c r="N15" s="368">
-        <f>L15+K15</f>
+        <f>K15+L15+M15</f>
         <v/>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       <c r="F16" s="365" t="n"/>
       <c r="G16" s="365" t="n"/>
       <c r="H16" s="367">
-        <f>F16+E16</f>
+        <f>E16+F16+G16</f>
         <v/>
       </c>
       <c r="I16" s="365" t="n"/>
@@ -8886,7 +8886,7 @@
       <c r="L16" s="365" t="n"/>
       <c r="M16" s="365" t="n"/>
       <c r="N16" s="368">
-        <f>L16+K16</f>
+        <f>K16+L16+M16</f>
         <v/>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       <c r="F17" s="365" t="n"/>
       <c r="G17" s="365" t="n"/>
       <c r="H17" s="367">
-        <f>F17+E17</f>
+        <f>E17+F17+G17</f>
         <v/>
       </c>
       <c r="I17" s="365" t="n"/>
@@ -8922,7 +8922,7 @@
       <c r="L17" s="365" t="n"/>
       <c r="M17" s="365" t="n"/>
       <c r="N17" s="368">
-        <f>L17+K17</f>
+        <f>K17+L17+M17</f>
         <v/>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       <c r="F18" s="365" t="n"/>
       <c r="G18" s="365" t="n"/>
       <c r="H18" s="367">
-        <f>F18+E18</f>
+        <f>E18+F18+G18</f>
         <v/>
       </c>
       <c r="I18" s="365" t="n"/>
@@ -8958,7 +8958,7 @@
       <c r="L18" s="365" t="n"/>
       <c r="M18" s="365" t="n"/>
       <c r="N18" s="368">
-        <f>L18+K18</f>
+        <f>K18+L18+M18</f>
         <v/>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       <c r="F19" s="365" t="n"/>
       <c r="G19" s="365" t="n"/>
       <c r="H19" s="367">
-        <f>F19+E19</f>
+        <f>E19+F19+G19</f>
         <v/>
       </c>
       <c r="I19" s="365" t="n"/>
@@ -8994,7 +8994,7 @@
       <c r="L19" s="365" t="n"/>
       <c r="M19" s="365" t="n"/>
       <c r="N19" s="368">
-        <f>L19+K19</f>
+        <f>K19+L19+M19</f>
         <v/>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       <c r="F20" s="365" t="n"/>
       <c r="G20" s="365" t="n"/>
       <c r="H20" s="367">
-        <f>F20+E20</f>
+        <f>E20+F20+G20</f>
         <v/>
       </c>
       <c r="I20" s="365" t="n"/>
@@ -9030,7 +9030,7 @@
       <c r="L20" s="365" t="n"/>
       <c r="M20" s="365" t="n"/>
       <c r="N20" s="368">
-        <f>L20+K20</f>
+        <f>K20+L20+M20</f>
         <v/>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       <c r="F21" s="365" t="n"/>
       <c r="G21" s="365" t="n"/>
       <c r="H21" s="367">
-        <f>F21+E21</f>
+        <f>E21+F21+G21</f>
         <v/>
       </c>
       <c r="I21" s="365" t="n"/>
@@ -9066,7 +9066,7 @@
       <c r="L21" s="365" t="n"/>
       <c r="M21" s="365" t="n"/>
       <c r="N21" s="368">
-        <f>L21+K21</f>
+        <f>K21+L21+M21</f>
         <v/>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
       <c r="F22" s="365" t="n"/>
       <c r="G22" s="365" t="n"/>
       <c r="H22" s="367">
-        <f>F22+E22</f>
+        <f>E22+F22+G22</f>
         <v/>
       </c>
       <c r="I22" s="365" t="n"/>
@@ -9098,7 +9098,7 @@
       <c r="L22" s="365" t="n"/>
       <c r="M22" s="365" t="n"/>
       <c r="N22" s="368">
-        <f>L22+K22</f>
+        <f>K22+L22+M22</f>
         <v/>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       <c r="F23" s="365" t="n"/>
       <c r="G23" s="365" t="n"/>
       <c r="H23" s="367">
-        <f>F23+E23</f>
+        <f>E23+F23+G23</f>
         <v/>
       </c>
       <c r="I23" s="365" t="n"/>
@@ -9134,7 +9134,7 @@
       <c r="L23" s="365" t="n"/>
       <c r="M23" s="365" t="n"/>
       <c r="N23" s="368">
-        <f>L23+K23</f>
+        <f>K23+L23+M23</f>
         <v/>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       <c r="F24" s="365" t="n"/>
       <c r="G24" s="365" t="n"/>
       <c r="H24" s="367">
-        <f>F24+E24</f>
+        <f>E24+F24+G24</f>
         <v/>
       </c>
       <c r="I24" s="365" t="n"/>
@@ -9166,7 +9166,7 @@
       <c r="L24" s="365" t="n"/>
       <c r="M24" s="365" t="n"/>
       <c r="N24" s="368">
-        <f>L24+K24</f>
+        <f>K24+L24+M24</f>
         <v/>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       <c r="F25" s="365" t="n"/>
       <c r="G25" s="365" t="n"/>
       <c r="H25" s="367">
-        <f>F25+E25</f>
+        <f>E25+F25+G25</f>
         <v/>
       </c>
       <c r="I25" s="365" t="n"/>
@@ -9202,7 +9202,7 @@
       <c r="L25" s="365" t="n"/>
       <c r="M25" s="365" t="n"/>
       <c r="N25" s="368">
-        <f>L25+K25</f>
+        <f>K25+L25+M25</f>
         <v/>
       </c>
     </row>
@@ -9226,7 +9226,7 @@
       <c r="F26" s="365" t="n"/>
       <c r="G26" s="365" t="n"/>
       <c r="H26" s="367">
-        <f>F26+E26</f>
+        <f>E26+F26+G26</f>
         <v/>
       </c>
       <c r="I26" s="365" t="n"/>
@@ -9238,7 +9238,7 @@
       <c r="L26" s="365" t="n"/>
       <c r="M26" s="365" t="n"/>
       <c r="N26" s="368">
-        <f>L26+K26</f>
+        <f>K26+L26+M26</f>
         <v/>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       <c r="F27" s="365" t="n"/>
       <c r="G27" s="365" t="n"/>
       <c r="H27" s="367">
-        <f>F27+E27</f>
+        <f>E27+F27+G27</f>
         <v/>
       </c>
       <c r="I27" s="365" t="n"/>
@@ -9274,7 +9274,7 @@
       <c r="L27" s="365" t="n"/>
       <c r="M27" s="365" t="n"/>
       <c r="N27" s="368">
-        <f>L27+K27</f>
+        <f>K27+L27+M27</f>
         <v/>
       </c>
     </row>
@@ -9294,7 +9294,7 @@
       <c r="F28" s="365" t="n"/>
       <c r="G28" s="365" t="n"/>
       <c r="H28" s="367">
-        <f>F28+E28</f>
+        <f>E28+F28+G28</f>
         <v/>
       </c>
       <c r="I28" s="365" t="n"/>
@@ -9306,7 +9306,7 @@
       <c r="L28" s="365" t="n"/>
       <c r="M28" s="365" t="n"/>
       <c r="N28" s="368">
-        <f>L28+K28</f>
+        <f>K28+L28+M28</f>
         <v/>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       <c r="F29" s="365" t="n"/>
       <c r="G29" s="365" t="n"/>
       <c r="H29" s="367">
-        <f>F29+E29</f>
+        <f>E29+F29+G29</f>
         <v/>
       </c>
       <c r="I29" s="365" t="n"/>
@@ -9338,7 +9338,7 @@
       <c r="L29" s="365" t="n"/>
       <c r="M29" s="365" t="n"/>
       <c r="N29" s="368">
-        <f>L29+K29</f>
+        <f>K29+L29+M29</f>
         <v/>
       </c>
     </row>
@@ -9362,7 +9362,7 @@
       <c r="F30" s="365" t="n"/>
       <c r="G30" s="365" t="n"/>
       <c r="H30" s="367">
-        <f>F30+E30</f>
+        <f>E30+F30+G30</f>
         <v/>
       </c>
       <c r="I30" s="365" t="n"/>
@@ -9374,7 +9374,7 @@
       <c r="L30" s="365" t="n"/>
       <c r="M30" s="365" t="n"/>
       <c r="N30" s="368">
-        <f>L30+K30</f>
+        <f>K30+L30+M30</f>
         <v/>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       <c r="F31" s="365" t="n"/>
       <c r="G31" s="365" t="n"/>
       <c r="H31" s="367">
-        <f>F31+E31</f>
+        <f>E31+F31+G31</f>
         <v/>
       </c>
       <c r="I31" s="365" t="n"/>
@@ -9410,7 +9410,7 @@
       <c r="L31" s="365" t="n"/>
       <c r="M31" s="365" t="n"/>
       <c r="N31" s="368">
-        <f>L31+K31</f>
+        <f>K31+L31+M31</f>
         <v/>
       </c>
     </row>
@@ -9434,7 +9434,7 @@
       <c r="F32" s="365" t="n"/>
       <c r="G32" s="365" t="n"/>
       <c r="H32" s="367">
-        <f>F32+E32</f>
+        <f>E32+F32+G32</f>
         <v/>
       </c>
       <c r="I32" s="365" t="n"/>
@@ -9446,7 +9446,7 @@
       <c r="L32" s="365" t="n"/>
       <c r="M32" s="365" t="n"/>
       <c r="N32" s="368">
-        <f>L32+K32</f>
+        <f>K32+L32+M32</f>
         <v/>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       <c r="F33" s="365" t="n"/>
       <c r="G33" s="365" t="n"/>
       <c r="H33" s="367">
-        <f>F33+E33</f>
+        <f>E33+F33+G33</f>
         <v/>
       </c>
       <c r="I33" s="365" t="n"/>
@@ -9482,7 +9482,7 @@
       <c r="L33" s="365" t="n"/>
       <c r="M33" s="365" t="n"/>
       <c r="N33" s="368">
-        <f>L33+K33</f>
+        <f>K33+L33+M33</f>
         <v/>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       <c r="F34" s="365" t="n"/>
       <c r="G34" s="365" t="n"/>
       <c r="H34" s="367">
-        <f>F34+E34</f>
+        <f>E34+F34+G34</f>
         <v/>
       </c>
       <c r="I34" s="365" t="n"/>
@@ -9518,7 +9518,7 @@
       <c r="L34" s="365" t="n"/>
       <c r="M34" s="365" t="n"/>
       <c r="N34" s="368">
-        <f>L34+K34</f>
+        <f>K34+L34+M34</f>
         <v/>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
       <c r="F35" s="365" t="n"/>
       <c r="G35" s="365" t="n"/>
       <c r="H35" s="367">
-        <f>F35+E35</f>
+        <f>E35+F35+G35</f>
         <v/>
       </c>
       <c r="I35" s="365" t="n"/>
@@ -9554,7 +9554,7 @@
       <c r="L35" s="365" t="n"/>
       <c r="M35" s="365" t="n"/>
       <c r="N35" s="368">
-        <f>L35+K35</f>
+        <f>K35+L35+M35</f>
         <v/>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       <c r="F36" s="365" t="n"/>
       <c r="G36" s="365" t="n"/>
       <c r="H36" s="367">
-        <f>F36+E36</f>
+        <f>E36+F36+G36</f>
         <v/>
       </c>
       <c r="I36" s="365" t="n"/>
@@ -9590,7 +9590,7 @@
       <c r="L36" s="365" t="n"/>
       <c r="M36" s="365" t="n"/>
       <c r="N36" s="368">
-        <f>L36+K36</f>
+        <f>K36+L36+M36</f>
         <v/>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       <c r="F37" s="365" t="n"/>
       <c r="G37" s="365" t="n"/>
       <c r="H37" s="367">
-        <f>F37+E37</f>
+        <f>E37+F37+G37</f>
         <v/>
       </c>
       <c r="I37" s="365" t="n"/>
@@ -9626,7 +9626,7 @@
       <c r="L37" s="365" t="n"/>
       <c r="M37" s="365" t="n"/>
       <c r="N37" s="368">
-        <f>L37+K37</f>
+        <f>K37+L37+M37</f>
         <v/>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       <c r="F38" s="365" t="n"/>
       <c r="G38" s="365" t="n"/>
       <c r="H38" s="367">
-        <f>F38+E38</f>
+        <f>E38+F38+G38</f>
         <v/>
       </c>
       <c r="I38" s="365" t="n"/>
@@ -9662,7 +9662,7 @@
       <c r="L38" s="365" t="n"/>
       <c r="M38" s="365" t="n"/>
       <c r="N38" s="368">
-        <f>L38+K38</f>
+        <f>K38+L38+M38</f>
         <v/>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       <c r="F39" s="365" t="n"/>
       <c r="G39" s="365" t="n"/>
       <c r="H39" s="367">
-        <f>F39+E39</f>
+        <f>E39+F39+G39</f>
         <v/>
       </c>
       <c r="I39" s="365" t="n"/>
@@ -9698,7 +9698,7 @@
       <c r="L39" s="365" t="n"/>
       <c r="M39" s="365" t="n"/>
       <c r="N39" s="368">
-        <f>L39+K39</f>
+        <f>K39+L39+M39</f>
         <v/>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       <c r="F40" s="365" t="n"/>
       <c r="G40" s="365" t="n"/>
       <c r="H40" s="367">
-        <f>F40+E40</f>
+        <f>E40+F40+G40</f>
         <v/>
       </c>
       <c r="I40" s="365" t="n"/>
@@ -9730,7 +9730,7 @@
       <c r="L40" s="365" t="n"/>
       <c r="M40" s="365" t="n"/>
       <c r="N40" s="368">
-        <f>L40+K40</f>
+        <f>K40+L40+M40</f>
         <v/>
       </c>
     </row>
@@ -9766,7 +9766,9 @@
         <f>SUM(F11:F41)</f>
         <v/>
       </c>
-      <c r="G42" s="367" t="n"/>
+      <c r="G42" s="367">
+        <f>SUM(G11:G41)</f>
+      </c>
       <c r="H42" s="367">
         <f>SUM(H11:H41)</f>
         <v/>
@@ -9784,7 +9786,9 @@
         <f>SUM(L11:L41)</f>
         <v/>
       </c>
-      <c r="M42" s="367" t="n"/>
+      <c r="M42" s="367">
+        <f>SUM(M11:M41)</f>
+      </c>
       <c r="N42" s="367">
         <f>SUM(N11:N41)</f>
         <v/>
